--- a/GameData/DataTables/Business/ZoneShrinkConfig.xlsx
+++ b/GameData/DataTables/Business/ZoneShrinkConfig.xlsx
@@ -1,18 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <bookViews>
-    <workbookView/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>#</t>
   </si>
@@ -59,40 +57,37 @@
     <t>Note</t>
   </si>
   <si>
-    <t>阶段名（Phase0_Slow / Phase1_Offset / Phase2_Rush）</t>
-  </si>
-  <si>
-    <t>本阶段进入时刻（秒，Run 启动 0 起）</t>
-  </si>
-  <si>
-    <t>本阶段持续时长（秒）</t>
-  </si>
-  <si>
-    <t>本阶段结束时的目标半径（米）</t>
+    <t>阶段名（Shrink1 / Shrink2 / Shrink3 / Shrink4）</t>
+  </si>
+  <si>
+    <t>缩圈活动内局部起始时间（秒）</t>
+  </si>
+  <si>
+    <t>正常模式缩圈时长（秒；快速模式由 MatchTiming 配置）</t>
+  </si>
+  <si>
+    <t>本次缩圈结束时的目标半径（米）</t>
   </si>
   <si>
     <t>圈外伤害（HP/s）</t>
   </si>
   <si>
-    <t>圈心偏移模式（None / Drift / Fixed），MVP 仅 None</t>
+    <t>圈心偏移模式（第一版仅 None）</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>Phase0_Slow</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>180.0</t>
-  </si>
-  <si>
-    <t>65.0</t>
-  </si>
-  <si>
-    <t>2.0</t>
+    <t>Shrink1</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>None</t>
@@ -101,34 +96,31 @@
     <t>1</t>
   </si>
   <si>
-    <t>Phase1_Offset</t>
-  </si>
-  <si>
-    <t>360.0</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>Drift</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Phase2_Rush</t>
-  </si>
-  <si>
-    <t>540.0</t>
-  </si>
-  <si>
-    <t>12.0</t>
-  </si>
-  <si>
-    <t>Fixed</t>
+    <t>Shrink2</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Shrink3</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Shrink4</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -159,207 +151,522 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+  <a:themeElements>
+    <a:clrScheme name="ChatGPT">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="ChatGPT">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" ht="105.599998474121" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" ht="52.7999992370605" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="0" t="s">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="0" t="s">
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="I6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="0" t="s">
+      <c r="I7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>38</v>
+      <c r="I8" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <tableParts count="1"/>
 </worksheet>
 </file>